--- a/wooclap/imports/optional/02_History_Part_2_optional.xlsx
+++ b/wooclap/imports/optional/02_History_Part_2_optional.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$2</definedName>
@@ -517,32 +517,32 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L00-O02 · What was AlphaGo famous for?</t>
+          <t>L00-O02 · AlphaGo combined learned components with search. Which conclusion is best supported by its success?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Introducing the first electronic calculator.</t>
+          <t>Learning made search unnecessary once enough games had been observed.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Writing the original proposal for the Turing test.</t>
+          <t>Combining learning with structured search can be powerful on a well-defined task without proving general intelligence.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Playing the board game Go at a very high level.</t>
+          <t>Beating expert players shows that the same system can solve unrelated intellectual tasks.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Being the first system to send an email.</t>
+          <t>Once a system outperforms humans, the method and task boundaries no longer matter.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
